--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA486A0-4016-4BD7-9AA3-56B98C58C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE0A5B5-3189-486D-80EC-52D6DC22E2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -79,7 +79,7 @@
   </si>
   <si>
     <t>{
-	"$schema": "http:\/\/json-schema.org\/draft-07\/schema#",
+	"$schema": "http://json-schema.org/draft-07/schema#",
 	"description": "MOSIP Sample identity",
 	"additionalProperties": false,
 	"title": "MOSIP identity",
@@ -150,88 +150,54 @@
 			"type": "object",
 			"required": [
 				"IDSchemaVersion",
-				"fullName",
+				"firstName",
+				"surname",
 				"dateOfBirth",
 				"gender",
 				"addressLine1",
 				"addressLine2",
-				"addressLine3",
-				"region",
-				"province",
-				"city",
-				"zone",
-				"postalCode",
-				"phone",
-				"email",
-				"proofOfIdentity",
+				"country",
+				"island",
+				"district",
+				"town",
+				"municipality",
 				"individualBiometrics"
 			],
 			"properties": {
 				"proofOfAddress": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/documentType"
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/documentType"
 				},
 				"gender": {
-					"bioAttributes": [
-					],
+					"bioAttributes": [],
 					"fieldCategory": "pvt",
 					"format": "",
 					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
-				},
-				"city": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^(?=.{0,50}$).*",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
-				},
-				"postalCode": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^[(?i)A-Z0-9]{5}$|^NA$",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"type": "string",
-					"fieldType": "default"
+					"$ref": "#/definitions/simpleType"
+				},
+				"country": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(?=.{0,50}$).*",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
 				},
 				"proofOfException-1": {
-					"bioAttributes": [
-					],
+					"bioAttributes": [],
 					"fieldCategory": "evidence",
 					"format": "none",
 					"fieldType": "default",
-					"$ref": "#\/definitions\/documentType"
-				},
-				"referenceIdentityNumber": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^([0-9]{10,30})$",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
-					"fieldCategory": "pvt",
-					"format": "kyc",
-					"type": "string",
-					"fieldType": "default"
+					"$ref": "#/definitions/documentType"
 				},
 				"individualBiometrics": {
 					"bioAttributes": [
@@ -252,43 +218,113 @@
 					"fieldCategory": "pvt",
 					"format": "none",
 					"fieldType": "default",
-					"$ref": "#\/definitions\/biometricsType"
-				},
-				"province": {
+					"$ref": "#/definitions/biometricsType"
+				},
+				"island": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(?=.{0,50}$).*",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"district": {
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"town": {
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"municipality": {
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"proofOfDateOfBirth": {
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/documentType"
+				},
+				"addressLine1": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(?=.{0,50}$).*",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"email": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"height": {
 					"bioAttributes": [
 					],
 					"validators": [{
-						"validator": "^(?=.{0,50}$).*",
+						"validator": "^[0-9]{1,3}$",
 						"arguments": [
 						],
 						"type": "regex"
 					}],
 					"fieldCategory": "pvt",
 					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"countryOfCitizenship": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"maritalStatus": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
 					"fieldType": "default",
 					"$ref": "#\/definitions\/simpleType"
 				},
-				"zone": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
-				},
-				"proofOfDateOfBirth": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/documentType"
-				},
-				"addressLine1": {
+				"fatherName": {
 					"bioAttributes": [
 					],
 					"validators": [{
-						"validator": "^(?=.{0,50}$).*",
+						"validator": "^(?=.{2,50}$).*",
 						"arguments": [
 						],
 						"type": "regex"
@@ -298,11 +334,11 @@
 					"fieldType": "default",
 					"$ref": "#\/definitions\/simpleType"
 				},
-				"addressLine2": {
+				"motherName": {
 					"bioAttributes": [
 					],
 					"validators": [{
-						"validator": "^(?=.{3,50}$).*",
+						"validator": "^(?=.{2,50}$).*",
 						"arguments": [
 						],
 						"type": "regex"
@@ -320,37 +356,8 @@
 					"fieldType": "default",
 					"$ref": "#\/definitions\/simpleType"
 				},
-				"addressLine3": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^(?=.{3,50}$).*",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
-				},
-				"email": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"type": "string",
-					"fieldType": "default"
-				},
 				"introducerRID": {
-					"bioAttributes": [
-					],
+					"bioAttributes": [],
 					"fieldCategory": "evidence",
 					"format": "none",
 					"type": "string",
@@ -375,31 +382,45 @@
 					"fieldCategory": "pvt",
 					"format": "none",
 					"fieldType": "default",
-					"$ref": "#\/definitions\/biometricsType"
-				},
-				"fullName": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^(?=.{3,50}$).*",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
+					"$ref": "#/definitions/biometricsType"
+				},
+				"firstName": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(?=.{3,50}$).*",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"surname": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(?=.{3,50}$).*",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
 				},
 				"dateOfBirth": {
-					"bioAttributes": [
-					],
-					"validators": [{
-						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])\/([0][1-9]|1[0-2])\/([0][1-9]|[1-2][0-9]|3[01])$",
-						"arguments": [
-						],
-						"type": "regex"
-					}],
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
 					"fieldCategory": "pvt",
 					"format": "none",
 					"type": "string",
@@ -424,27 +445,24 @@
 					"fieldCategory": "pvt",
 					"format": "none",
 					"fieldType": "default",
-					"$ref": "#\/definitions\/biometricsType"
+					"$ref": "#/definitions/biometricsType"
 				},
 				"introducerUIN": {
-					"bioAttributes": [
-					],
+					"bioAttributes": [],
 					"fieldCategory": "evidence",
 					"format": "none",
 					"type": "string",
 					"fieldType": "default"
 				},
 				"proofOfIdentity": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/documentType"
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/documentType"
 				},
 				"IDSchemaVersion": {
-					"bioAttributes": [
-					],
+					"bioAttributes": [],
 					"fieldCategory": "none",
 					"format": "none",
 					"type": "number",
@@ -452,18 +470,17 @@
 					"minimum": 0
 				},
 				"proofOfException": {
-					"bioAttributes": [
-					],
+					"bioAttributes": [],
 					"fieldCategory": "evidence",
 					"format": "none",
 					"fieldType": "default",
-					"$ref": "#\/definitions\/documentType"
-				},
-				"phone": {
+					"$ref": "#/definitions/documentType"
+				},
+				"mobileNumber": {
 					"bioAttributes": [
 					],
 					"validators": [{
-						"validator": "^[+]*([0-9]{1})([0-9]{9})$",
+						"validator": "^\\+239\\s?[0-9]{7}$",
 						"arguments": [
 						],
 						"type": "regex"
@@ -473,51 +490,77 @@
 					"type": "string",
 					"fieldType": "default"
 				},
-				"introducerName": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "evidence",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
-				},
-				"proofOfRelationship": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/documentType"
-				},
-				"UIN": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "none",
-					"format": "none",
-					"type": "string",
-					"fieldType": "default"
-				},
-				"preferredLang": {
-					"bioAttributes": [
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"type": "string",
-					"fieldType": "dynamic"
-				},
-				"region": {
+				"passportNumber": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "kyc",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"passportIssuingCountry": {
+					"bioAttributes": [
+					],
+					"fieldCategory": "kyc",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"passportDateOfIssue": {
 					"bioAttributes": [
 					],
 					"validators": [{
-						"validator": "^(?=.{0,50}$).*",
+						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])\/([0][1-9]|1[0-2])\/([0][1-9]|[1-2][0-9]|3[01])$",
 						"arguments": [
 						],
 						"type": "regex"
 					}],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#\/definitions\/simpleType"
+					"fieldCategory": "kyc",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"passportDateOfExpiry": {
+					"bioAttributes": [
+					],
+					"validators": [{
+						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])\/([0][1-9]|1[0-2])\/([0][1-9]|[1-2][0-9]|3[01])$",
+						"arguments": [
+						],
+						"type": "regex"
+					}],
+					"fieldCategory": "kyc",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"introducerName": {
+					"bioAttributes": [],
+					"fieldCategory": "evidence",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
+				"proofOfRelationship": {
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/documentType"
+				},
+				"UIN": {
+					"bioAttributes": [],
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"preferredLang": {
+					"bioAttributes": [],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"type": "string",
+					"fieldType": "dynamic"
 				}
 			}
 		}
@@ -541,7 +584,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -614,9 +657,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -654,7 +697,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -760,7 +803,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -902,7 +945,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -918,8 +961,8 @@
     <col min="3" max="3" width="11.54296875" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.453125" style="1"/>
     <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="53.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53.81640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.453125" style="2" customWidth="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.453125" style="2"/>

--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE0A5B5-3189-486D-80EC-52D6DC22E2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3F5598-810E-4413-B385-5A3125208622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -156,7 +156,6 @@
 				"gender",
 				"addressLine1",
 				"addressLine2",
-				"country",
 				"island",
 				"district",
 				"town",
@@ -175,20 +174,6 @@
 					"bioAttributes": [],
 					"fieldCategory": "pvt",
 					"format": "",
-					"fieldType": "default",
-					"$ref": "#/definitions/simpleType"
-				},
-				"country": {
-					"bioAttributes": [],
-					"validators": [
-						{
-							"validator": "^(?=.{0,50}$).*",
-							"arguments": [],
-							"type": "regex"
-						}
-					],
-					"fieldCategory": "pvt",
-					"format": "none",
 					"fieldType": "default",
 					"$ref": "#/definitions/simpleType"
 				},

--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3F5598-810E-4413-B385-5A3125208622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7C1BCB-805B-4E3F-87C6-5A2E980F3BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,6 +154,8 @@
 				"surname",
 				"dateOfBirth",
 				"gender",
+				"countryOfCitizenship",
+				"maritalStatus",
 				"addressLine1",
 				"addressLine2",
 				"island",
@@ -295,7 +297,8 @@
 					"fieldCategory": "pvt",
 					"format": "none",
 					"type": "string",
-					"fieldType": "default"
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
 				},
 				"maritalStatus": {
 					"bioAttributes": [
@@ -489,7 +492,8 @@
 					"fieldCategory": "kyc",
 					"format": "none",
 					"type": "string",
-					"fieldType": "default"
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
 				},
 				"passportDateOfIssue": {
 					"bioAttributes": [

--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7C1BCB-805B-4E3F-87C6-5A2E980F3BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0513EEED-A200-4360-AB06-972A567D8B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,13 +179,6 @@
 					"fieldType": "default",
 					"$ref": "#/definitions/simpleType"
 				},
-				"proofOfException-1": {
-					"bioAttributes": [],
-					"fieldCategory": "evidence",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#/definitions/documentType"
-				},
 				"individualBiometrics": {
 					"bioAttributes": [
 						"leftEye",
@@ -263,6 +256,20 @@
 					"fieldType": "default",
 					"$ref": "#/definitions/simpleType"
 				},
+				"addressLine2": {
+					"bioAttributes": [],
+					"validators": [
+						{
+							"validator": "^(?=.{0,50}$).*",
+							"arguments": [],
+							"type": "regex"
+						}
+					],
+					"fieldCategory": "pvt",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#/definitions/simpleType"
+				},
 				"email": {
 					"bioAttributes": [],
 					"validators": [
@@ -296,7 +303,6 @@
 					],
 					"fieldCategory": "pvt",
 					"format": "none",
-					"type": "string",
 					"fieldType": "default",
 					"$ref": "#\/definitions\/simpleType"
 				},

--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0513EEED-A200-4360-AB06-972A567D8B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D48FB5-B25F-492B-8113-55CD93EF338F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,13 +165,6 @@
 				"individualBiometrics"
 			],
 			"properties": {
-				"proofOfAddress": {
-					"bioAttributes": [],
-					"fieldCategory": "pvt",
-					"format": "none",
-					"fieldType": "default",
-					"$ref": "#/definitions/documentType"
-				},
 				"gender": {
 					"bioAttributes": [],
 					"fieldCategory": "pvt",
